--- a/data/cuaca_yogyakarta.xlsx
+++ b/data/cuaca_yogyakarta.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,23 +486,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22.9</v>
+        <v>25.7</v>
       </c>
       <c r="D2" t="n">
-        <v>28</v>
+        <v>29.9</v>
       </c>
       <c r="E2" t="n">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>5.7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -513,14 +513,152 @@
         <v>30.2</v>
       </c>
       <c r="J2" t="n">
-        <v>22.9</v>
+        <v>23.5</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>Gerimis Sedang</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>82</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Gerimis Sedang</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>94</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Cerah Sebagian</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Gerimis Ringan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>52</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Gerimis Ringan</t>
         </is>
       </c>
     </row>

--- a/data/cuaca_yogyakarta.xlsx
+++ b/data/cuaca_yogyakarta.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,11 +486,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="D2" t="n">
         <v>29.9</v>
@@ -502,7 +502,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -527,28 +527,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25.6</v>
+        <v>30.6</v>
       </c>
       <c r="D3" t="n">
-        <v>29.9</v>
+        <v>33.5</v>
       </c>
       <c r="E3" t="n">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>5.3</v>
+        <v>7.9</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -556,107 +556,15 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>30.2</v>
+        <v>31.3</v>
       </c>
       <c r="J3" t="n">
-        <v>23.5</v>
+        <v>21.4</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="L3" t="inlineStr">
-        <is>
-          <t>Gerimis Sedang</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>07:01</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="D4" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>94</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Cerah Sebagian</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="J4" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Gerimis Ringan</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="D5" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>52</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Mendung</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="J5" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L5" t="inlineStr">
         <is>
           <t>Gerimis Ringan</t>
         </is>

--- a/data/cuaca_yogyakarta.xlsx
+++ b/data/cuaca_yogyakarta.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cuaca" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cuaca" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/cuaca_yogyakarta.xlsx
+++ b/data/cuaca_yogyakarta.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,6 +567,236 @@
       <c r="L3" t="inlineStr">
         <is>
           <t>Gerimis Ringan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E4" t="n">
+        <v>88</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>07:03</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="D5" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>88</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>07:03</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="D6" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>88</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>88</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>85</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Cerah</t>
         </is>
       </c>
     </row>

--- a/data/cuaca_yogyakarta.xlsx
+++ b/data/cuaca_yogyakarta.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,7 +670,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>07:03</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -711,90 +711,44 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>07:05</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.9</v>
+        <v>21.4</v>
       </c>
       <c r="D7" t="n">
-        <v>23.6</v>
+        <v>24.2</v>
       </c>
       <c r="E7" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Mendung</t>
+          <t>Cerah</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>30.5</v>
+        <v>31.6</v>
       </c>
       <c r="J7" t="n">
-        <v>20.9</v>
+        <v>21.4</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="inlineStr">
-        <is>
-          <t>Mendung</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="D8" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>85</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Cerah</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr">
         <is>
           <t>Cerah</t>
         </is>

--- a/data/cuaca_yogyakarta.xlsx
+++ b/data/cuaca_yogyakarta.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -751,6 +751,52 @@
       <c r="L7" t="inlineStr">
         <is>
           <t>Cerah</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>23:56</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>88</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>22</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Mendung</t>
         </is>
       </c>
     </row>

--- a/data/cuaca_yogyakarta.xlsx
+++ b/data/cuaca_yogyakarta.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +797,52 @@
       <c r="L8" t="inlineStr">
         <is>
           <t>Mendung</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>89</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>31</v>
+      </c>
+      <c r="J9" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Gerimis Ringan</t>
         </is>
       </c>
     </row>

--- a/data/cuaca_yogyakarta.xlsx
+++ b/data/cuaca_yogyakarta.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -846,6 +846,98 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>07:03</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E10" t="n">
+        <v>91</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>07:04</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>91</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/cuaca_yogyakarta.xlsx
+++ b/data/cuaca_yogyakarta.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -938,6 +938,98 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>83</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Cerah Sebagian</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>72</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/cuaca_yogyakarta.xlsx
+++ b/data/cuaca_yogyakarta.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,6 +1030,880 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>61</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>33</v>
+      </c>
+      <c r="E15" t="n">
+        <v>50</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>44</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="D17" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>44</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="D18" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>48</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Gerimis Ringan</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>27</v>
+      </c>
+      <c r="D19" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>65</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Gerimis Ringan</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>27</v>
+      </c>
+      <c r="D20" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>65</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Gerimis Ringan</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>71</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Gerimis Ringan</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E22" t="n">
+        <v>71</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Gerimis Ringan</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>22:01</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>78</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="J23" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Gerimis Ringan</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>00:02</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E24" t="n">
+        <v>88</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>02:01</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>91</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Cerah Sebagian</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>02:03</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>91</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Cerah Sebagian</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>04:01</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E27" t="n">
+        <v>78</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Cerah Sebagian</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="D28" t="n">
+        <v>23</v>
+      </c>
+      <c r="E28" t="n">
+        <v>81</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Cerah Sebagian</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Cerah Sebagian</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="D29" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>82</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Cerah Sebagian</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Cerah Sebagian</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="D30" t="n">
+        <v>24</v>
+      </c>
+      <c r="E30" t="n">
+        <v>78</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="J30" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Cerah Sebagian</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="D31" t="n">
+        <v>24</v>
+      </c>
+      <c r="E31" t="n">
+        <v>78</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Cerah Sebagian</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E32" t="n">
+        <v>70</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/cuaca_yogyakarta.xlsx
+++ b/data/cuaca_yogyakarta.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1904,6 +1904,144 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="E33" t="n">
+        <v>75</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="J33" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="D34" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E34" t="n">
+        <v>72</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="D35" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E35" t="n">
+        <v>93</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="J35" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Cerah Sebagian</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/cuaca_yogyakarta.xlsx
+++ b/data/cuaca_yogyakarta.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2042,6 +2042,282 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="D36" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>93</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>33</v>
+      </c>
+      <c r="J36" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="D37" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="E37" t="n">
+        <v>43</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="J37" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="D38" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E38" t="n">
+        <v>65</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>33</v>
+      </c>
+      <c r="J38" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="D39" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>87</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="J39" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Cerah Sebagian</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="D40" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="E40" t="n">
+        <v>39</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>7</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="J40" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Cerah Sebagian</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="D41" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="E41" t="n">
+        <v>71</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="J41" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Cerah Sebagian</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/cuaca_yogyakarta.xlsx
+++ b/data/cuaca_yogyakarta.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2318,6 +2318,1018 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>22</v>
+      </c>
+      <c r="D42" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E42" t="n">
+        <v>83</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="J42" t="n">
+        <v>22</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Gerimis Ringan</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>32</v>
+      </c>
+      <c r="D43" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>45</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="J43" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Gerimis Ringan</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E44" t="n">
+        <v>70</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="J44" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Gerimis Ringan</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="D45" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E45" t="n">
+        <v>91</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="J45" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="E46" t="n">
+        <v>41</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="J46" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D47" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="E47" t="n">
+        <v>69</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="J47" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>21</v>
+      </c>
+      <c r="D48" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E48" t="n">
+        <v>87</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="J48" t="n">
+        <v>21</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Gerimis Ringan</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="D49" t="n">
+        <v>36</v>
+      </c>
+      <c r="E49" t="n">
+        <v>40</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Gerimis Ringan</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="D50" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="E50" t="n">
+        <v>70</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Cerah Sebagian</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="J50" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Gerimis Ringan</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="D51" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E51" t="n">
+        <v>87</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Cerah Sebagian</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="J51" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="E52" t="n">
+        <v>48</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Cerah Sebagian</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Gerimis Ringan</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="D53" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="E53" t="n">
+        <v>72</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="J53" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Gerimis Ringan</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="D54" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E54" t="n">
+        <v>87</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="J54" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Gerimis Ringan</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="E55" t="n">
+        <v>43</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="J55" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Gerimis Ringan</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>26</v>
+      </c>
+      <c r="D56" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>73</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="J56" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Gerimis Ringan</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E57" t="n">
+        <v>85</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="J57" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="D58" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E58" t="n">
+        <v>44</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Cerah Sebagian</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>31</v>
+      </c>
+      <c r="J58" t="n">
+        <v>21</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="D59" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="E59" t="n">
+        <v>67</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>31</v>
+      </c>
+      <c r="J59" t="n">
+        <v>21</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Gerimis Ringan</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="D60" t="n">
+        <v>24</v>
+      </c>
+      <c r="E60" t="n">
+        <v>90</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="J60" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Gerimis Sedang</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="D61" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E61" t="n">
+        <v>51</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G61" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Gerimis Ringan</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="J61" t="n">
+        <v>21</v>
+      </c>
+      <c r="K61" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Gerimis Sedang</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>25</v>
+      </c>
+      <c r="D62" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E62" t="n">
+        <v>69</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>10</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Mendung</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>29</v>
+      </c>
+      <c r="J62" t="n">
+        <v>21</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Gerimis Sedang</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="D63" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>89</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>3</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Cerah</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="J63" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Gerimis Ringan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
